--- a/public/exports-60-250-with-coowners/29188386.xlsx
+++ b/public/exports-60-250-with-coowners/29188386.xlsx
@@ -1939,7 +1939,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311405994</t>
+          <t xml:space="preserve">311405990</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
